--- a/Full-LC-AUTO/insights/image_folder_insight.xlsx
+++ b/Full-LC-AUTO/insights/image_folder_insight.xlsx
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -575,34 +575,34 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -611,35 +611,35 @@
           <t>Ice</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>7</v>
+      <c r="B3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -649,34 +649,34 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -685,34 +685,34 @@
           <t>Black-Plain</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,108 +722,145 @@
           <t>White-Plain</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Trouser</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>7</v>
+          <t>White-Baggy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Trouser</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Shorts</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -838,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -923,38 +960,38 @@
           <t>Beige</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>18</v>
+      <c r="B2" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -963,38 +1000,38 @@
           <t>Ice</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="C3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="J3" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>49</v>
+      <c r="K3" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -1003,38 +1040,38 @@
           <t>Black-baggy</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="B4" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>29</v>
+      <c r="I4" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1043,37 +1080,37 @@
           <t>Black-Plain</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1083,118 +1120,158 @@
           <t>White-Plain</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Trouser</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>74</v>
+          <t>White-Baggy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Trouser</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Shorts</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>2</v>
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1300,7 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Folder names under the configured image roots for ASUS</t>
+          <t>Folder names under the configured image roots for HP</t>
         </is>
       </c>
     </row>
@@ -1309,35 +1386,56 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Ice: skipped folder tokens in '1-FADE'f-FADE's-IND'f-STAR'f-STAR's - Aps' (Unknown brand code 'Aps' in folder '1-FADE'f-FADE's-IND'f-STAR'f-STAR's - Aps')</t>
+          <t>Shorts: skipped folder 'BEIGE' (Folder name must start with a number: BEIGE)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ice: skipped folder tokens in '2-FADE'f-FADE's-IND'f-STAR'f-STAR's - As' (Unknown brand code 'As' in folder '2-FADE'f-FADE's-IND'f-STAR'f-STAR's - As')</t>
+          <t>Shorts: skipped folder 'Black-baggy' (Folder name must start with a number: Black-baggy)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Ice: skipped folder tokens in '3-FADE'f-FADE's-IND'f-STAR'f-STAR's - As' (Unknown brand code 'As' in folder '3-FADE'f-FADE's-IND'f-STAR'f-STAR's - As')</t>
+          <t>Shorts: skipped folder 'Black-Plain' (Folder name must start with a number: Black-Plain)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Trouser: skipped folder tokens in '1-FADE'f-FADE's-GENZ'f-GENZ's-IND'f-IND's-STAR'f-STAR's - Aps' (Unknown brand code 'Aps' in folder '1-FADE'f-FADE's-GENZ'f-GENZ's-IND'f-IND's-STAR'f-STAR's - Aps')</t>
+          <t>Shorts: skipped folder 'ICE' (Folder name must start with a number: ICE)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Trouser: skipped folder tokens in '2-FADE'f-FADE's-GENZ'f-GENZ's-IND'f-IND's-STAR'f-STAR's -Aps' (Unknown brand code 'Aps' in folder '2-FADE'f-FADE's-GENZ'f-GENZ's-IND'f-IND's-STAR'f-STAR's -Aps')</t>
+          <t>Shorts: skipped folder 'Shorts' (Folder name must start with a number: Shorts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Shorts: skipped folder 'Trouser' (Folder name must start with a number: Trouser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Shorts: skipped folder 'White' (Folder name must start with a number: White)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Shorts: skipped folder 'White-baggy' (Folder name must start with a number: White-baggy)</t>
         </is>
       </c>
     </row>
